--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,6 +930,1304 @@
           <t>Eftersök av arter i områden där de inte tidigare är hittade</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129490714</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91318</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Haraån, Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>472905</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6991197</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129490126</v>
+      </c>
+      <c r="B5" t="n">
+        <v>88945</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>510</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Haraån, Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>472976</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6991172</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129490826</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91565</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Haraån, Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>472881</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6991194</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129490498</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91541</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Haraån, Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>472965</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6991226</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129489773</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Haraån, Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>472910</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6991140</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 individ</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129489731</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91545</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Haraån, Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>472913</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6991135</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129489495</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97583</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Haraån, Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>472872</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6991094</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129490557</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91318</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Haraån, Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>472950</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6991212</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129490374</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98712</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Haraån, Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>472983</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6991195</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129491374</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91318</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Haraån, Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>472729</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6991022</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129491023</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97583</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Haraån, Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>472840</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6991159</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129491664</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98712</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nattjärnen, Nattjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>472699</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6990981</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>129490714</v>
       </c>
       <c r="B4" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>129490126</v>
       </c>
       <c r="B5" t="n">
-        <v>88945</v>
+        <v>88949</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>129490826</v>
       </c>
       <c r="B6" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129490498</v>
       </c>
       <c r="B7" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>129489731</v>
       </c>
       <c r="B9" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>129489495</v>
       </c>
       <c r="B10" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,45 +1683,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129490557</v>
+        <v>129490374</v>
       </c>
       <c r="B11" t="n">
-        <v>91318</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472950</v>
+        <v>472983</v>
       </c>
       <c r="R11" t="n">
-        <v>6991212</v>
+        <v>6991195</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,54 +1799,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129490374</v>
+        <v>129490557</v>
       </c>
       <c r="B12" t="n">
-        <v>98712</v>
+        <v>91322</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472983</v>
+        <v>472950</v>
       </c>
       <c r="R12" t="n">
-        <v>6991195</v>
+        <v>6991212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,7 +1909,7 @@
         <v>129491374</v>
       </c>
       <c r="B13" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,48 +2013,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129491023</v>
+        <v>129491664</v>
       </c>
       <c r="B14" t="n">
-        <v>97583</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Nattjärnen, Nattjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472840</v>
+        <v>472699</v>
       </c>
       <c r="R14" t="n">
-        <v>6991159</v>
+        <v>6990981</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2083,7 +2087,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,64 +2112,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129491664</v>
+        <v>129491023</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>97587</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nattjärnen, Nattjärnen, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472699</v>
+        <v>472840</v>
       </c>
       <c r="R15" t="n">
-        <v>6990981</v>
+        <v>6991159</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,12 +2219,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>129490714</v>
       </c>
       <c r="B4" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>129490126</v>
       </c>
       <c r="B5" t="n">
-        <v>88949</v>
+        <v>88950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>129490826</v>
       </c>
       <c r="B6" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129490498</v>
       </c>
       <c r="B7" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>129489731</v>
       </c>
       <c r="B9" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>129489495</v>
       </c>
       <c r="B10" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>129490374</v>
       </c>
       <c r="B11" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>129490557</v>
       </c>
       <c r="B12" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>129491374</v>
       </c>
       <c r="B13" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>129491664</v>
       </c>
       <c r="B14" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>129491023</v>
       </c>
       <c r="B15" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -1683,54 +1683,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129490374</v>
+        <v>129490557</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>91323</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472983</v>
+        <v>472950</v>
       </c>
       <c r="R11" t="n">
-        <v>6991195</v>
+        <v>6991212</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1762,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,7 +1790,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129490557</v>
+        <v>129491374</v>
       </c>
       <c r="B12" t="n">
         <v>91323</v>
@@ -1834,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472950</v>
+        <v>472729</v>
       </c>
       <c r="R12" t="n">
-        <v>6991212</v>
+        <v>6991022</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1879,7 +1870,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,45 +1897,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129491374</v>
+        <v>129490374</v>
       </c>
       <c r="B13" t="n">
-        <v>91323</v>
+        <v>98724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472729</v>
+        <v>472983</v>
       </c>
       <c r="R13" t="n">
-        <v>6991022</v>
+        <v>6991195</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,52 +2013,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129491664</v>
+        <v>129491023</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>97595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nattjärnen, Nattjärnen, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472699</v>
+        <v>472840</v>
       </c>
       <c r="R14" t="n">
-        <v>6990981</v>
+        <v>6991159</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2087,7 +2083,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2097,7 +2093,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,60 +2108,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129491023</v>
+        <v>129491664</v>
       </c>
       <c r="B15" t="n">
-        <v>97595</v>
+        <v>98724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Nattjärnen, Nattjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472840</v>
+        <v>472699</v>
       </c>
       <c r="R15" t="n">
-        <v>6991159</v>
+        <v>6990981</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,12 +2219,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>129490714</v>
       </c>
       <c r="B4" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>129490126</v>
       </c>
       <c r="B5" t="n">
-        <v>88950</v>
+        <v>88952</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>129490826</v>
       </c>
       <c r="B6" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129490498</v>
       </c>
       <c r="B7" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>129489731</v>
       </c>
       <c r="B9" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>129489495</v>
       </c>
       <c r="B10" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>129490557</v>
       </c>
       <c r="B11" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>129491374</v>
       </c>
       <c r="B12" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>129490374</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,48 +2013,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129491023</v>
+        <v>129491664</v>
       </c>
       <c r="B14" t="n">
-        <v>97595</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Nattjärnen, Nattjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472840</v>
+        <v>472699</v>
       </c>
       <c r="R14" t="n">
-        <v>6991159</v>
+        <v>6990981</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2083,7 +2087,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,64 +2112,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129491664</v>
+        <v>129491023</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>97598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nattjärnen, Nattjärnen, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472699</v>
+        <v>472840</v>
       </c>
       <c r="R15" t="n">
-        <v>6990981</v>
+        <v>6991159</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,12 +2219,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -2013,52 +2013,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129491664</v>
+        <v>129491023</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>97598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nattjärnen, Nattjärnen, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472699</v>
+        <v>472840</v>
       </c>
       <c r="R14" t="n">
-        <v>6990981</v>
+        <v>6991159</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2087,7 +2083,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2097,7 +2093,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,60 +2108,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129491023</v>
+        <v>129491664</v>
       </c>
       <c r="B15" t="n">
-        <v>97598</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Nattjärnen, Nattjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472840</v>
+        <v>472699</v>
       </c>
       <c r="R15" t="n">
-        <v>6991159</v>
+        <v>6990981</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,12 +2219,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -2013,48 +2013,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129491023</v>
+        <v>129491664</v>
       </c>
       <c r="B14" t="n">
-        <v>97598</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Nattjärnen, Nattjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472840</v>
+        <v>472699</v>
       </c>
       <c r="R14" t="n">
-        <v>6991159</v>
+        <v>6990981</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2083,7 +2087,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,64 +2112,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129491664</v>
+        <v>129491023</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>97598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nattjärnen, Nattjärnen, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472699</v>
+        <v>472840</v>
       </c>
       <c r="R15" t="n">
-        <v>6990981</v>
+        <v>6991159</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,12 +2219,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -1683,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129490557</v>
+        <v>129491374</v>
       </c>
       <c r="B11" t="n">
         <v>91326</v>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472950</v>
+        <v>472729</v>
       </c>
       <c r="R11" t="n">
-        <v>6991212</v>
+        <v>6991022</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,7 +1790,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129491374</v>
+        <v>129490557</v>
       </c>
       <c r="B12" t="n">
         <v>91326</v>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472729</v>
+        <v>472950</v>
       </c>
       <c r="R12" t="n">
-        <v>6991022</v>
+        <v>6991212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2013,52 +2013,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129491664</v>
+        <v>129491023</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>97598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nattjärnen, Nattjärnen, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472699</v>
+        <v>472840</v>
       </c>
       <c r="R14" t="n">
-        <v>6990981</v>
+        <v>6991159</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2087,7 +2083,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2097,7 +2093,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,60 +2108,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129491023</v>
+        <v>129491664</v>
       </c>
       <c r="B15" t="n">
-        <v>97598</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Nattjärnen, Nattjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472840</v>
+        <v>472699</v>
       </c>
       <c r="R15" t="n">
-        <v>6991159</v>
+        <v>6990981</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,12 +2219,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>129490714</v>
       </c>
       <c r="B4" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>129490126</v>
       </c>
       <c r="B5" t="n">
-        <v>88952</v>
+        <v>88980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>129490826</v>
       </c>
       <c r="B6" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129490498</v>
       </c>
       <c r="B7" t="n">
-        <v>91549</v>
+        <v>91577</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>129489773</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>129489731</v>
       </c>
       <c r="B9" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>129489495</v>
       </c>
       <c r="B10" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129491374</v>
+        <v>129490557</v>
       </c>
       <c r="B11" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472729</v>
+        <v>472950</v>
       </c>
       <c r="R11" t="n">
-        <v>6991022</v>
+        <v>6991212</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129490557</v>
+        <v>129491374</v>
       </c>
       <c r="B12" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472950</v>
+        <v>472729</v>
       </c>
       <c r="R12" t="n">
-        <v>6991212</v>
+        <v>6991022</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,7 +1900,7 @@
         <v>129490374</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,48 +2013,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129491023</v>
+        <v>129491664</v>
       </c>
       <c r="B14" t="n">
-        <v>97598</v>
+        <v>98756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Nattjärnen, Nattjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472840</v>
+        <v>472699</v>
       </c>
       <c r="R14" t="n">
-        <v>6991159</v>
+        <v>6990981</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2083,7 +2087,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,64 +2112,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129491664</v>
+        <v>129491023</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>97627</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nattjärnen, Nattjärnen, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472699</v>
+        <v>472840</v>
       </c>
       <c r="R15" t="n">
-        <v>6990981</v>
+        <v>6991159</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,12 +2219,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,7 +936,7 @@
         <v>129490714</v>
       </c>
       <c r="B4" t="n">
-        <v>91354</v>
+        <v>91360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>129490126</v>
       </c>
       <c r="B5" t="n">
-        <v>88980</v>
+        <v>88986</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>129490826</v>
       </c>
       <c r="B6" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129490498</v>
       </c>
       <c r="B7" t="n">
-        <v>91577</v>
+        <v>91583</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>129489773</v>
       </c>
       <c r="B8" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>129489731</v>
       </c>
       <c r="B9" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>129489495</v>
       </c>
       <c r="B10" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>129490557</v>
       </c>
       <c r="B11" t="n">
-        <v>91354</v>
+        <v>91360</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>129491374</v>
       </c>
       <c r="B12" t="n">
-        <v>91354</v>
+        <v>91360</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>129490374</v>
       </c>
       <c r="B13" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,52 +2013,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129491664</v>
+        <v>129491023</v>
       </c>
       <c r="B14" t="n">
-        <v>98756</v>
+        <v>97639</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nattjärnen, Nattjärnen, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472699</v>
+        <v>472840</v>
       </c>
       <c r="R14" t="n">
-        <v>6990981</v>
+        <v>6991159</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2087,7 +2083,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2097,7 +2093,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,60 +2108,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129491023</v>
+        <v>129491664</v>
       </c>
       <c r="B15" t="n">
-        <v>97627</v>
+        <v>98768</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Nattjärnen, Nattjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472840</v>
+        <v>472699</v>
       </c>
       <c r="R15" t="n">
-        <v>6991159</v>
+        <v>6990981</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,15 +2219,4838 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129762583</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>472863</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6991225</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129762584</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>472871</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6991227</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129762624</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>472644</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6990960</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 41 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129762577</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>472802</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6991188</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129762575</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>472795</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6991181</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129762585</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>472867</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6991229</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129762566</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>472716</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6991137</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129762579</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>472826</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6991202</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129762634</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>472947</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6991126</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>I en stående död gran med full längd.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129762558</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92305</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>472797</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6991042</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I granstubbe.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129762574</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>472779</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6991172</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129762582</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>472849</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6991219</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska och äldre, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129762589</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>472883</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6991239</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129762586</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>472881</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6991231</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på två granstammar nära varann vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129762657</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>472840</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6991061</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en gran bland andra hänglavar.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129762568</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>472720</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6991143</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129762622</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>472814</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6991112</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor inom ca 1 m2 yta i gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129762570</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>472725</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6991144</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129762578</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>472809</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6991191</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129762563</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>472656</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6991102</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129762633</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>472927</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6991209</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>I en stående död gran med full längd och som har potentiella födosökspår efter tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129762590</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>472886</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6991239</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129762580</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>472840</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6991212</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129762573</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>472776</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6991166</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129762565</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>472694</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6991118</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, äldre, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129762581</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>472842</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6991214</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129762569</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>472728</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6991144</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129762576</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>472792</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6991185</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129762591</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>472892</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6991241</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129762571</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>472735</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6991146</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129762564</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>472675</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6991111</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129762567</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>472722</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6991139</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129762587</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>472879</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6991236</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, i riklig mängd på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129762588</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>472882</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6991235</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129762592</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>472887</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6991241</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>129490714</v>
       </c>
       <c r="B4" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>129490126</v>
       </c>
       <c r="B5" t="n">
-        <v>88986</v>
+        <v>88987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>129490826</v>
       </c>
       <c r="B6" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129490498</v>
       </c>
       <c r="B7" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>129489773</v>
       </c>
       <c r="B8" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>129489731</v>
       </c>
       <c r="B9" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>129489495</v>
       </c>
       <c r="B10" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>129490557</v>
       </c>
       <c r="B11" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>129491374</v>
       </c>
       <c r="B12" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>129490374</v>
       </c>
       <c r="B13" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,48 +2013,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129491023</v>
+        <v>129491664</v>
       </c>
       <c r="B14" t="n">
-        <v>97639</v>
+        <v>98769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Nattjärnen, Nattjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472840</v>
+        <v>472699</v>
       </c>
       <c r="R14" t="n">
-        <v>6991159</v>
+        <v>6990981</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2083,7 +2087,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,64 +2112,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129491664</v>
+        <v>129491023</v>
       </c>
       <c r="B15" t="n">
-        <v>98768</v>
+        <v>97640</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nattjärnen, Nattjärnen, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472699</v>
+        <v>472840</v>
       </c>
       <c r="R15" t="n">
-        <v>6990981</v>
+        <v>6991159</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,12 +2219,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2234,7 +2234,7 @@
         <v>129762583</v>
       </c>
       <c r="B16" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,42 +2370,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129762584</v>
+        <v>129762624</v>
       </c>
       <c r="B17" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2417,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472871</v>
+        <v>472644</v>
       </c>
       <c r="R17" t="n">
-        <v>6991227</v>
+        <v>6990960</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,7 +2465,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 41 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2466,32 +2474,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2509,50 +2498,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129762624</v>
+        <v>129762584</v>
       </c>
       <c r="B18" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2564,10 +2545,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472644</v>
+        <v>472871</v>
       </c>
       <c r="R18" t="n">
-        <v>6990960</v>
+        <v>6991227</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2604,7 +2585,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 41 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,13 +2594,32 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2640,7 +2640,7 @@
         <v>129762577</v>
       </c>
       <c r="B19" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>129762575</v>
       </c>
       <c r="B20" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>129762585</v>
       </c>
       <c r="B21" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>129762566</v>
       </c>
       <c r="B22" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129762579</v>
       </c>
       <c r="B23" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>129762634</v>
       </c>
       <c r="B24" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>129762558</v>
       </c>
       <c r="B25" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>129762574</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>129762582</v>
       </c>
       <c r="B27" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>129762589</v>
       </c>
       <c r="B28" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>129762586</v>
       </c>
       <c r="B29" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129762657</v>
+        <v>129762568</v>
       </c>
       <c r="B30" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4169,37 +4169,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472840</v>
+        <v>472720</v>
       </c>
       <c r="R30" t="n">
-        <v>6991061</v>
+        <v>6991143</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4236,7 +4245,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På en gran bland andra hänglavar.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4245,13 +4254,12 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4266,12 +4274,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4289,10 +4297,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129762568</v>
+        <v>129762657</v>
       </c>
       <c r="B31" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4300,46 +4308,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472720</v>
+        <v>472840</v>
       </c>
       <c r="R31" t="n">
-        <v>6991143</v>
+        <v>6991061</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4376,7 +4375,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>På en gran bland andra hänglavar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4385,12 +4384,13 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4431,7 +4431,7 @@
         <v>129762622</v>
       </c>
       <c r="B32" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>129762570</v>
       </c>
       <c r="B33" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>129762578</v>
       </c>
       <c r="B34" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>129762563</v>
       </c>
       <c r="B35" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>129762633</v>
       </c>
       <c r="B36" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>129762590</v>
       </c>
       <c r="B37" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>129762580</v>
       </c>
       <c r="B38" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>129762573</v>
       </c>
       <c r="B39" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>129762565</v>
       </c>
       <c r="B40" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>129762581</v>
       </c>
       <c r="B41" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>129762569</v>
       </c>
       <c r="B42" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>129762576</v>
       </c>
       <c r="B43" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>129762591</v>
       </c>
       <c r="B44" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>129762571</v>
       </c>
       <c r="B45" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>129762564</v>
       </c>
       <c r="B46" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>129762567</v>
       </c>
       <c r="B47" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>129762587</v>
       </c>
       <c r="B48" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>129762588</v>
       </c>
       <c r="B49" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>129762592</v>
       </c>
       <c r="B50" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -2370,50 +2370,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129762624</v>
+        <v>129762584</v>
       </c>
       <c r="B17" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2425,10 +2417,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472644</v>
+        <v>472871</v>
       </c>
       <c r="R17" t="n">
-        <v>6990960</v>
+        <v>6991227</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,7 +2457,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 41 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2474,13 +2466,32 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2498,7 +2509,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129762584</v>
+        <v>129762577</v>
       </c>
       <c r="B18" t="n">
         <v>57736</v>
@@ -2545,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472871</v>
+        <v>472802</v>
       </c>
       <c r="R18" t="n">
-        <v>6991227</v>
+        <v>6991188</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,42 +2648,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762577</v>
+        <v>129762624</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>98769</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2684,10 +2703,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472802</v>
+        <v>472644</v>
       </c>
       <c r="R19" t="n">
-        <v>6991188</v>
+        <v>6990960</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2724,7 +2743,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 41 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,32 +2752,13 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>129490714</v>
       </c>
       <c r="B4" t="n">
-        <v>91361</v>
+        <v>91366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>129490126</v>
       </c>
       <c r="B5" t="n">
-        <v>88987</v>
+        <v>88992</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>129490826</v>
       </c>
       <c r="B6" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129490498</v>
       </c>
       <c r="B7" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>129489731</v>
       </c>
       <c r="B9" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>129489495</v>
       </c>
       <c r="B10" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>129490557</v>
       </c>
       <c r="B11" t="n">
-        <v>91361</v>
+        <v>91366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>129491374</v>
       </c>
       <c r="B12" t="n">
-        <v>91361</v>
+        <v>91366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>129490374</v>
       </c>
       <c r="B13" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>129491664</v>
       </c>
       <c r="B14" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>129491023</v>
       </c>
       <c r="B15" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>129762624</v>
       </c>
       <c r="B19" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3332,32 +3332,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129762634</v>
+        <v>129762558</v>
       </c>
       <c r="B24" t="n">
-        <v>91584</v>
+        <v>92311</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472947</v>
+        <v>472797</v>
       </c>
       <c r="R24" t="n">
-        <v>6991126</v>
+        <v>6991042</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>I granstubbe.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3467,32 +3467,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129762558</v>
+        <v>129762634</v>
       </c>
       <c r="B25" t="n">
-        <v>92306</v>
+        <v>91589</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472797</v>
+        <v>472947</v>
       </c>
       <c r="R25" t="n">
-        <v>6991042</v>
+        <v>6991126</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I granstubbe.</t>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129762568</v>
+        <v>129762657</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4169,46 +4169,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472720</v>
+        <v>472840</v>
       </c>
       <c r="R30" t="n">
-        <v>6991143</v>
+        <v>6991061</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4245,7 +4236,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>På en gran bland andra hänglavar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4254,12 +4245,13 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4274,12 +4266,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4297,10 +4289,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129762657</v>
+        <v>129762568</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4308,37 +4300,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472840</v>
+        <v>472720</v>
       </c>
       <c r="R31" t="n">
-        <v>6991061</v>
+        <v>6991143</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4375,7 +4376,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en gran bland andra hänglavar.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4384,13 +4385,12 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4431,7 +4431,7 @@
         <v>129762622</v>
       </c>
       <c r="B32" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>129762633</v>
       </c>
       <c r="B36" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -2013,52 +2013,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129491664</v>
+        <v>129491023</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>97645</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nattjärnen, Nattjärnen, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472699</v>
+        <v>472840</v>
       </c>
       <c r="R14" t="n">
-        <v>6990981</v>
+        <v>6991159</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2087,7 +2083,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2097,7 +2093,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,60 +2108,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129491023</v>
+        <v>129491664</v>
       </c>
       <c r="B15" t="n">
-        <v>97645</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Nattjärnen, Nattjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472840</v>
+        <v>472699</v>
       </c>
       <c r="R15" t="n">
-        <v>6991159</v>
+        <v>6990981</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,12 +2219,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129762657</v>
+        <v>129762568</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4169,37 +4169,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472840</v>
+        <v>472720</v>
       </c>
       <c r="R30" t="n">
-        <v>6991061</v>
+        <v>6991143</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4236,7 +4245,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På en gran bland andra hänglavar.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4245,13 +4254,12 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4266,12 +4274,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4289,10 +4297,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129762568</v>
+        <v>129762657</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4300,46 +4308,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472720</v>
+        <v>472840</v>
       </c>
       <c r="R31" t="n">
-        <v>6991143</v>
+        <v>6991061</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4376,7 +4375,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>På en gran bland andra hänglavar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4385,12 +4384,13 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4973,10 +4973,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762633</v>
+        <v>129762590</v>
       </c>
       <c r="B36" t="n">
-        <v>91589</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4984,41 +4984,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472927</v>
+        <v>472886</v>
       </c>
       <c r="R36" t="n">
-        <v>6991209</v>
+        <v>6991239</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5055,7 +5060,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd och som har potentiella födosökspår efter tretåig hackspett.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5064,7 +5069,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5085,12 +5089,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5108,10 +5112,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129762590</v>
+        <v>129762633</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>91589</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5119,46 +5123,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472886</v>
+        <v>472927</v>
       </c>
       <c r="R37" t="n">
-        <v>6991239</v>
+        <v>6991209</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5195,7 +5194,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>I en stående död gran med full längd och som har potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5204,6 +5203,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5224,12 +5224,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -4297,48 +4297,65 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129762657</v>
+        <v>129762622</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472840</v>
+        <v>472814</v>
       </c>
       <c r="R31" t="n">
-        <v>6991061</v>
+        <v>6991112</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4375,7 +4392,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en gran bland andra hänglavar.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4390,27 +4407,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4428,65 +4425,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129762622</v>
+        <v>129762657</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472814</v>
+        <v>472840</v>
       </c>
       <c r="R32" t="n">
-        <v>6991112</v>
+        <v>6991061</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4523,7 +4503,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta i gammal granskog.</t>
+          <t>På en gran bland andra hänglavar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4538,7 +4518,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4973,10 +4973,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762590</v>
+        <v>129762633</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>91589</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4984,46 +4984,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472886</v>
+        <v>472927</v>
       </c>
       <c r="R36" t="n">
-        <v>6991239</v>
+        <v>6991209</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5060,7 +5055,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>I en stående död gran med full längd och som har potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5069,6 +5064,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5089,12 +5085,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5112,10 +5108,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129762633</v>
+        <v>129762590</v>
       </c>
       <c r="B37" t="n">
-        <v>91589</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5123,41 +5119,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472927</v>
+        <v>472886</v>
       </c>
       <c r="R37" t="n">
-        <v>6991209</v>
+        <v>6991239</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5194,7 +5195,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd och som har potentiella födosökspår efter tretåig hackspett.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5203,7 +5204,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5224,12 +5224,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -6498,7 +6498,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129762567</v>
+        <v>129762592</v>
       </c>
       <c r="B47" t="n">
         <v>57736</v>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>472722</v>
+        <v>472887</v>
       </c>
       <c r="R47" t="n">
-        <v>6991139</v>
+        <v>6991241</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6637,7 +6637,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129762587</v>
+        <v>129762567</v>
       </c>
       <c r="B48" t="n">
         <v>57736</v>
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>472879</v>
+        <v>472722</v>
       </c>
       <c r="R48" t="n">
-        <v>6991236</v>
+        <v>6991139</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6776,7 +6776,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129762588</v>
+        <v>129762587</v>
       </c>
       <c r="B49" t="n">
         <v>57736</v>
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>472882</v>
+        <v>472879</v>
       </c>
       <c r="R49" t="n">
-        <v>6991235</v>
+        <v>6991236</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack/savhack, färska, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6915,7 +6915,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129762592</v>
+        <v>129762588</v>
       </c>
       <c r="B50" t="n">
         <v>57736</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>472887</v>
+        <v>472882</v>
       </c>
       <c r="R50" t="n">
-        <v>6991241</v>
+        <v>6991235</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -3332,32 +3332,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129762558</v>
+        <v>129762634</v>
       </c>
       <c r="B24" t="n">
-        <v>92311</v>
+        <v>91589</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472797</v>
+        <v>472947</v>
       </c>
       <c r="R24" t="n">
-        <v>6991042</v>
+        <v>6991126</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>I granstubbe.</t>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3467,32 +3467,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129762634</v>
+        <v>129762558</v>
       </c>
       <c r="B25" t="n">
-        <v>91589</v>
+        <v>92311</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472947</v>
+        <v>472797</v>
       </c>
       <c r="R25" t="n">
-        <v>6991126</v>
+        <v>6991042</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>I granstubbe.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129762568</v>
+        <v>129762657</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4169,46 +4169,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472720</v>
+        <v>472840</v>
       </c>
       <c r="R30" t="n">
-        <v>6991143</v>
+        <v>6991061</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4245,7 +4236,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>På en gran bland andra hänglavar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4254,12 +4245,13 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4274,12 +4266,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4297,50 +4289,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129762622</v>
+        <v>129762568</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4352,10 +4336,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472814</v>
+        <v>472720</v>
       </c>
       <c r="R31" t="n">
-        <v>6991112</v>
+        <v>6991143</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4392,7 +4376,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4401,13 +4385,32 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4425,48 +4428,65 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129762657</v>
+        <v>129762622</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472840</v>
+        <v>472814</v>
       </c>
       <c r="R32" t="n">
-        <v>6991061</v>
+        <v>6991112</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4503,7 +4523,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en gran bland andra hänglavar.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4518,27 +4538,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4973,10 +4973,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762633</v>
+        <v>129762590</v>
       </c>
       <c r="B36" t="n">
-        <v>91589</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4984,41 +4984,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472927</v>
+        <v>472886</v>
       </c>
       <c r="R36" t="n">
-        <v>6991209</v>
+        <v>6991239</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5055,7 +5060,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd och som har potentiella födosökspår efter tretåig hackspett.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5064,7 +5069,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5085,12 +5089,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5108,10 +5112,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129762590</v>
+        <v>129762633</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>91589</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5119,46 +5123,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472886</v>
+        <v>472927</v>
       </c>
       <c r="R37" t="n">
-        <v>6991239</v>
+        <v>6991209</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5195,7 +5194,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>I en stående död gran med full längd och som har potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5204,6 +5203,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5224,12 +5224,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -6498,7 +6498,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129762592</v>
+        <v>129762567</v>
       </c>
       <c r="B47" t="n">
         <v>57736</v>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>472887</v>
+        <v>472722</v>
       </c>
       <c r="R47" t="n">
-        <v>6991241</v>
+        <v>6991139</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6637,7 +6637,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129762567</v>
+        <v>129762587</v>
       </c>
       <c r="B48" t="n">
         <v>57736</v>
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>472722</v>
+        <v>472879</v>
       </c>
       <c r="R48" t="n">
-        <v>6991139</v>
+        <v>6991236</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack/savhack, färska, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6776,7 +6776,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129762587</v>
+        <v>129762588</v>
       </c>
       <c r="B49" t="n">
         <v>57736</v>
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>472879</v>
+        <v>472882</v>
       </c>
       <c r="R49" t="n">
-        <v>6991236</v>
+        <v>6991235</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6915,7 +6915,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129762588</v>
+        <v>129762592</v>
       </c>
       <c r="B50" t="n">
         <v>57736</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>472882</v>
+        <v>472887</v>
       </c>
       <c r="R50" t="n">
-        <v>6991235</v>
+        <v>6991241</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>129490714</v>
       </c>
       <c r="B4" t="n">
-        <v>91366</v>
+        <v>91370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>129490126</v>
       </c>
       <c r="B5" t="n">
-        <v>88992</v>
+        <v>88996</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>129490826</v>
       </c>
       <c r="B6" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129490498</v>
       </c>
       <c r="B7" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>129489731</v>
       </c>
       <c r="B9" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>129489495</v>
       </c>
       <c r="B10" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>129490557</v>
       </c>
       <c r="B11" t="n">
-        <v>91366</v>
+        <v>91370</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>129491374</v>
       </c>
       <c r="B12" t="n">
-        <v>91366</v>
+        <v>91370</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>129490374</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,48 +2013,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129491023</v>
+        <v>129491664</v>
       </c>
       <c r="B14" t="n">
-        <v>97645</v>
+        <v>98778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Nattjärnen, Nattjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472840</v>
+        <v>472699</v>
       </c>
       <c r="R14" t="n">
-        <v>6991159</v>
+        <v>6990981</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2083,7 +2087,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,64 +2112,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129491664</v>
+        <v>129491023</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>97649</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nattjärnen, Nattjärnen, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472699</v>
+        <v>472840</v>
       </c>
       <c r="R15" t="n">
-        <v>6990981</v>
+        <v>6991159</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,12 +2219,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
         <v>129762624</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762575</v>
+        <v>129762585</v>
       </c>
       <c r="B20" t="n">
         <v>57736</v>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472795</v>
+        <v>472867</v>
       </c>
       <c r="R20" t="n">
-        <v>6991181</v>
+        <v>6991229</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762585</v>
+        <v>129762566</v>
       </c>
       <c r="B21" t="n">
         <v>57736</v>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472867</v>
+        <v>472716</v>
       </c>
       <c r="R21" t="n">
-        <v>6991229</v>
+        <v>6991137</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762566</v>
+        <v>129762575</v>
       </c>
       <c r="B22" t="n">
         <v>57736</v>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472716</v>
+        <v>472795</v>
       </c>
       <c r="R22" t="n">
-        <v>6991137</v>
+        <v>6991181</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3335,7 +3335,7 @@
         <v>129762634</v>
       </c>
       <c r="B24" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>129762558</v>
       </c>
       <c r="B25" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>129762622</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129762570</v>
+        <v>129762578</v>
       </c>
       <c r="B33" t="n">
         <v>57736</v>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472725</v>
+        <v>472809</v>
       </c>
       <c r="R33" t="n">
-        <v>6991144</v>
+        <v>6991191</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129762578</v>
+        <v>129762570</v>
       </c>
       <c r="B34" t="n">
         <v>57736</v>
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472809</v>
+        <v>472725</v>
       </c>
       <c r="R34" t="n">
-        <v>6991191</v>
+        <v>6991144</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4973,10 +4973,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762590</v>
+        <v>129762633</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4984,46 +4984,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472886</v>
+        <v>472927</v>
       </c>
       <c r="R36" t="n">
-        <v>6991239</v>
+        <v>6991209</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5060,7 +5055,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>I en stående död gran med full längd och som har potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5069,6 +5064,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5089,12 +5085,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5112,10 +5108,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129762633</v>
+        <v>129762590</v>
       </c>
       <c r="B37" t="n">
-        <v>91589</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5123,41 +5119,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472927</v>
+        <v>472886</v>
       </c>
       <c r="R37" t="n">
-        <v>6991209</v>
+        <v>6991239</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5194,7 +5195,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd och som har potentiella födosökspår efter tretåig hackspett.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5203,7 +5204,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5224,12 +5224,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129762580</v>
+        <v>129762573</v>
       </c>
       <c r="B38" t="n">
         <v>57736</v>
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472840</v>
+        <v>472776</v>
       </c>
       <c r="R38" t="n">
-        <v>6991212</v>
+        <v>6991166</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129762573</v>
+        <v>129762580</v>
       </c>
       <c r="B39" t="n">
         <v>57736</v>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472776</v>
+        <v>472840</v>
       </c>
       <c r="R39" t="n">
-        <v>6991166</v>
+        <v>6991212</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -6498,7 +6498,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129762567</v>
+        <v>129762592</v>
       </c>
       <c r="B47" t="n">
         <v>57736</v>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>472722</v>
+        <v>472887</v>
       </c>
       <c r="R47" t="n">
-        <v>6991139</v>
+        <v>6991241</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6637,7 +6637,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129762587</v>
+        <v>129762567</v>
       </c>
       <c r="B48" t="n">
         <v>57736</v>
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>472879</v>
+        <v>472722</v>
       </c>
       <c r="R48" t="n">
-        <v>6991236</v>
+        <v>6991139</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6776,7 +6776,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129762588</v>
+        <v>129762587</v>
       </c>
       <c r="B49" t="n">
         <v>57736</v>
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>472882</v>
+        <v>472879</v>
       </c>
       <c r="R49" t="n">
-        <v>6991235</v>
+        <v>6991236</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack/savhack, färska, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6915,7 +6915,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129762592</v>
+        <v>129762588</v>
       </c>
       <c r="B50" t="n">
         <v>57736</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>472887</v>
+        <v>472882</v>
       </c>
       <c r="R50" t="n">
-        <v>6991241</v>
+        <v>6991235</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>129490714</v>
       </c>
       <c r="B4" t="n">
-        <v>91370</v>
+        <v>91372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>129490126</v>
       </c>
       <c r="B5" t="n">
-        <v>88996</v>
+        <v>88998</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>129490826</v>
       </c>
       <c r="B6" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129490498</v>
       </c>
       <c r="B7" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>129489731</v>
       </c>
       <c r="B9" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>129489495</v>
       </c>
       <c r="B10" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>129490557</v>
       </c>
       <c r="B11" t="n">
-        <v>91370</v>
+        <v>91372</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>129491374</v>
       </c>
       <c r="B12" t="n">
-        <v>91370</v>
+        <v>91372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>129490374</v>
       </c>
       <c r="B13" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>129491664</v>
       </c>
       <c r="B14" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>129491023</v>
       </c>
       <c r="B15" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>129762624</v>
       </c>
       <c r="B19" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762585</v>
+        <v>129762575</v>
       </c>
       <c r="B20" t="n">
         <v>57736</v>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472867</v>
+        <v>472795</v>
       </c>
       <c r="R20" t="n">
-        <v>6991229</v>
+        <v>6991181</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762566</v>
+        <v>129762585</v>
       </c>
       <c r="B21" t="n">
         <v>57736</v>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472716</v>
+        <v>472867</v>
       </c>
       <c r="R21" t="n">
-        <v>6991137</v>
+        <v>6991229</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762575</v>
+        <v>129762566</v>
       </c>
       <c r="B22" t="n">
         <v>57736</v>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472795</v>
+        <v>472716</v>
       </c>
       <c r="R22" t="n">
-        <v>6991181</v>
+        <v>6991137</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3335,7 +3335,7 @@
         <v>129762634</v>
       </c>
       <c r="B24" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>129762558</v>
       </c>
       <c r="B25" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>129762622</v>
       </c>
       <c r="B32" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129762578</v>
+        <v>129762570</v>
       </c>
       <c r="B33" t="n">
         <v>57736</v>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472809</v>
+        <v>472725</v>
       </c>
       <c r="R33" t="n">
-        <v>6991191</v>
+        <v>6991144</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129762570</v>
+        <v>129762578</v>
       </c>
       <c r="B34" t="n">
         <v>57736</v>
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472725</v>
+        <v>472809</v>
       </c>
       <c r="R34" t="n">
-        <v>6991144</v>
+        <v>6991191</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4976,7 +4976,7 @@
         <v>129762633</v>
       </c>
       <c r="B36" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129762573</v>
+        <v>129762580</v>
       </c>
       <c r="B38" t="n">
         <v>57736</v>
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472776</v>
+        <v>472840</v>
       </c>
       <c r="R38" t="n">
-        <v>6991166</v>
+        <v>6991212</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129762580</v>
+        <v>129762573</v>
       </c>
       <c r="B39" t="n">
         <v>57736</v>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472840</v>
+        <v>472776</v>
       </c>
       <c r="R39" t="n">
-        <v>6991212</v>
+        <v>6991166</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -6498,7 +6498,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129762592</v>
+        <v>129762567</v>
       </c>
       <c r="B47" t="n">
         <v>57736</v>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>472887</v>
+        <v>472722</v>
       </c>
       <c r="R47" t="n">
-        <v>6991241</v>
+        <v>6991139</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6637,7 +6637,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129762567</v>
+        <v>129762587</v>
       </c>
       <c r="B48" t="n">
         <v>57736</v>
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>472722</v>
+        <v>472879</v>
       </c>
       <c r="R48" t="n">
-        <v>6991139</v>
+        <v>6991236</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack/savhack, färska, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6776,7 +6776,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129762587</v>
+        <v>129762588</v>
       </c>
       <c r="B49" t="n">
         <v>57736</v>
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>472879</v>
+        <v>472882</v>
       </c>
       <c r="R49" t="n">
-        <v>6991236</v>
+        <v>6991235</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6915,7 +6915,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129762588</v>
+        <v>129762592</v>
       </c>
       <c r="B50" t="n">
         <v>57736</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>472882</v>
+        <v>472887</v>
       </c>
       <c r="R50" t="n">
-        <v>6991235</v>
+        <v>6991241</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -1683,45 +1683,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129490557</v>
+        <v>129490374</v>
       </c>
       <c r="B11" t="n">
-        <v>91372</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472950</v>
+        <v>472983</v>
       </c>
       <c r="R11" t="n">
-        <v>6991212</v>
+        <v>6991195</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,7 +1799,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129491374</v>
+        <v>129490557</v>
       </c>
       <c r="B12" t="n">
         <v>91372</v>
@@ -1825,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472729</v>
+        <v>472950</v>
       </c>
       <c r="R12" t="n">
-        <v>6991022</v>
+        <v>6991212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,7 +1869,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,7 +1879,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,54 +1906,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129490374</v>
+        <v>129491374</v>
       </c>
       <c r="B13" t="n">
-        <v>98780</v>
+        <v>91372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472983</v>
+        <v>472729</v>
       </c>
       <c r="R13" t="n">
-        <v>6991195</v>
+        <v>6991022</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -1579,7 +1579,7 @@
         <v>129489495</v>
       </c>
       <c r="B10" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>129490374</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>129491664</v>
       </c>
       <c r="B14" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>129491023</v>
       </c>
       <c r="B15" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>129762624</v>
       </c>
       <c r="B19" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762575</v>
+        <v>129762566</v>
       </c>
       <c r="B20" t="n">
         <v>57736</v>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472795</v>
+        <v>472716</v>
       </c>
       <c r="R20" t="n">
-        <v>6991181</v>
+        <v>6991137</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762585</v>
+        <v>129762575</v>
       </c>
       <c r="B21" t="n">
         <v>57736</v>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472867</v>
+        <v>472795</v>
       </c>
       <c r="R21" t="n">
-        <v>6991229</v>
+        <v>6991181</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762566</v>
+        <v>129762585</v>
       </c>
       <c r="B22" t="n">
         <v>57736</v>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472716</v>
+        <v>472867</v>
       </c>
       <c r="R22" t="n">
-        <v>6991137</v>
+        <v>6991229</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3332,32 +3332,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129762634</v>
+        <v>129762558</v>
       </c>
       <c r="B24" t="n">
-        <v>91595</v>
+        <v>92317</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472947</v>
+        <v>472797</v>
       </c>
       <c r="R24" t="n">
-        <v>6991126</v>
+        <v>6991042</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>I granstubbe.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3467,32 +3467,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129762558</v>
+        <v>129762634</v>
       </c>
       <c r="B25" t="n">
-        <v>92317</v>
+        <v>91595</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472797</v>
+        <v>472947</v>
       </c>
       <c r="R25" t="n">
-        <v>6991042</v>
+        <v>6991126</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I granstubbe.</t>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4289,42 +4289,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129762568</v>
+        <v>129762622</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>98790</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4336,10 +4344,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472720</v>
+        <v>472814</v>
       </c>
       <c r="R31" t="n">
-        <v>6991143</v>
+        <v>6991112</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4376,7 +4384,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4385,32 +4393,13 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4428,50 +4417,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129762622</v>
+        <v>129762568</v>
       </c>
       <c r="B32" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4483,10 +4464,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472814</v>
+        <v>472720</v>
       </c>
       <c r="R32" t="n">
-        <v>6991112</v>
+        <v>6991143</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4523,7 +4504,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4532,13 +4513,32 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -2776,7 +2776,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762566</v>
+        <v>129762575</v>
       </c>
       <c r="B20" t="n">
         <v>57736</v>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472716</v>
+        <v>472795</v>
       </c>
       <c r="R20" t="n">
-        <v>6991137</v>
+        <v>6991181</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762575</v>
+        <v>129762585</v>
       </c>
       <c r="B21" t="n">
         <v>57736</v>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472795</v>
+        <v>472867</v>
       </c>
       <c r="R21" t="n">
-        <v>6991181</v>
+        <v>6991229</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762585</v>
+        <v>129762566</v>
       </c>
       <c r="B22" t="n">
         <v>57736</v>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472867</v>
+        <v>472716</v>
       </c>
       <c r="R22" t="n">
-        <v>6991229</v>
+        <v>6991137</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -4158,48 +4158,65 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129762657</v>
+        <v>129762622</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472840</v>
+        <v>472814</v>
       </c>
       <c r="R30" t="n">
-        <v>6991061</v>
+        <v>6991112</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4236,7 +4253,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På en gran bland andra hänglavar.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4251,27 +4268,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4289,65 +4286,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129762622</v>
+        <v>129762657</v>
       </c>
       <c r="B31" t="n">
-        <v>98790</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472814</v>
+        <v>472840</v>
       </c>
       <c r="R31" t="n">
-        <v>6991112</v>
+        <v>6991061</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4384,7 +4364,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta i gammal granskog.</t>
+          <t>På en gran bland andra hänglavar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4399,7 +4379,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -2234,7 +2234,7 @@
         <v>129762583</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>129762584</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>129762577</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>129762624</v>
       </c>
       <c r="B19" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>129762575</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>129762585</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>129762566</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129762579</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>129762558</v>
       </c>
       <c r="B24" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>129762634</v>
       </c>
       <c r="B25" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>129762574</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>129762582</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>129762589</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>129762586</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4158,50 +4158,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129762622</v>
+        <v>129762568</v>
       </c>
       <c r="B30" t="n">
-        <v>98790</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4213,10 +4205,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472814</v>
+        <v>472720</v>
       </c>
       <c r="R30" t="n">
-        <v>6991112</v>
+        <v>6991143</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4253,7 +4245,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4262,13 +4254,32 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4289,7 +4300,7 @@
         <v>129762657</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4417,42 +4428,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129762568</v>
+        <v>129762622</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>98794</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4464,10 +4483,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472720</v>
+        <v>472814</v>
       </c>
       <c r="R32" t="n">
-        <v>6991143</v>
+        <v>6991112</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4504,7 +4523,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4513,32 +4532,13 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4559,7 +4559,7 @@
         <v>129762570</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>129762578</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>129762563</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>129762633</v>
       </c>
       <c r="B36" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>129762590</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>129762580</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>129762573</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>129762565</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>129762581</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>129762569</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>129762576</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>129762591</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>129762571</v>
       </c>
       <c r="B45" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>129762564</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>129762567</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>129762587</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>129762588</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>129762592</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -2776,7 +2776,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762575</v>
+        <v>129762566</v>
       </c>
       <c r="B20" t="n">
         <v>57737</v>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472795</v>
+        <v>472716</v>
       </c>
       <c r="R20" t="n">
-        <v>6991181</v>
+        <v>6991137</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762585</v>
+        <v>129762575</v>
       </c>
       <c r="B21" t="n">
         <v>57737</v>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472867</v>
+        <v>472795</v>
       </c>
       <c r="R21" t="n">
-        <v>6991229</v>
+        <v>6991181</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762566</v>
+        <v>129762585</v>
       </c>
       <c r="B22" t="n">
         <v>57737</v>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472716</v>
+        <v>472867</v>
       </c>
       <c r="R22" t="n">
-        <v>6991137</v>
+        <v>6991229</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3332,32 +3332,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129762558</v>
+        <v>129762634</v>
       </c>
       <c r="B24" t="n">
-        <v>92320</v>
+        <v>91598</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472797</v>
+        <v>472947</v>
       </c>
       <c r="R24" t="n">
-        <v>6991042</v>
+        <v>6991126</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>I granstubbe.</t>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3467,32 +3467,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129762634</v>
+        <v>129762558</v>
       </c>
       <c r="B25" t="n">
-        <v>91598</v>
+        <v>92320</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472947</v>
+        <v>472797</v>
       </c>
       <c r="R25" t="n">
-        <v>6991126</v>
+        <v>6991042</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>I granstubbe.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3880,7 +3880,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129762589</v>
+        <v>129762586</v>
       </c>
       <c r="B28" t="n">
         <v>57737</v>
@@ -3927,10 +3927,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472883</v>
+        <v>472881</v>
       </c>
       <c r="R28" t="n">
-        <v>6991239</v>
+        <v>6991231</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack/savhack, färska, på två granstammar nära varann vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4019,7 +4019,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129762586</v>
+        <v>129762589</v>
       </c>
       <c r="B29" t="n">
         <v>57737</v>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472881</v>
+        <v>472883</v>
       </c>
       <c r="R29" t="n">
-        <v>6991231</v>
+        <v>6991239</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på två granstammar nära varann vid hyggeskanten.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4297,48 +4297,65 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129762657</v>
+        <v>129762622</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>98794</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472840</v>
+        <v>472814</v>
       </c>
       <c r="R31" t="n">
-        <v>6991061</v>
+        <v>6991112</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4375,7 +4392,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en gran bland andra hänglavar.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4390,27 +4407,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4428,65 +4425,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129762622</v>
+        <v>129762657</v>
       </c>
       <c r="B32" t="n">
-        <v>98794</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472814</v>
+        <v>472840</v>
       </c>
       <c r="R32" t="n">
-        <v>6991112</v>
+        <v>6991061</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4523,7 +4503,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta i gammal granskog.</t>
+          <t>På en gran bland andra hänglavar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4538,7 +4518,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129762578</v>
+        <v>129762563</v>
       </c>
       <c r="B34" t="n">
         <v>57737</v>
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472809</v>
+        <v>472656</v>
       </c>
       <c r="R34" t="n">
-        <v>6991191</v>
+        <v>6991102</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4834,7 +4834,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129762563</v>
+        <v>129762578</v>
       </c>
       <c r="B35" t="n">
         <v>57737</v>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472656</v>
+        <v>472809</v>
       </c>
       <c r="R35" t="n">
-        <v>6991102</v>
+        <v>6991191</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4973,10 +4973,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762633</v>
+        <v>129762590</v>
       </c>
       <c r="B36" t="n">
-        <v>91598</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4984,41 +4984,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472927</v>
+        <v>472886</v>
       </c>
       <c r="R36" t="n">
-        <v>6991209</v>
+        <v>6991239</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5055,7 +5060,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd och som har potentiella födosökspår efter tretåig hackspett.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5064,7 +5069,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5085,12 +5089,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5108,10 +5112,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129762590</v>
+        <v>129762633</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>91598</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5119,46 +5123,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472886</v>
+        <v>472927</v>
       </c>
       <c r="R37" t="n">
-        <v>6991239</v>
+        <v>6991209</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5195,7 +5194,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>I en stående död gran med full längd och som har potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5204,6 +5203,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5224,12 +5224,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5664,7 +5664,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129762581</v>
+        <v>129762569</v>
       </c>
       <c r="B41" t="n">
         <v>57737</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>472842</v>
+        <v>472728</v>
       </c>
       <c r="R41" t="n">
-        <v>6991214</v>
+        <v>6991144</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5803,7 +5803,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129762569</v>
+        <v>129762581</v>
       </c>
       <c r="B42" t="n">
         <v>57737</v>
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472728</v>
+        <v>472842</v>
       </c>
       <c r="R42" t="n">
-        <v>6991144</v>
+        <v>6991214</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -2776,7 +2776,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762566</v>
+        <v>129762575</v>
       </c>
       <c r="B20" t="n">
         <v>57737</v>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472716</v>
+        <v>472795</v>
       </c>
       <c r="R20" t="n">
-        <v>6991137</v>
+        <v>6991181</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762575</v>
+        <v>129762585</v>
       </c>
       <c r="B21" t="n">
         <v>57737</v>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472795</v>
+        <v>472867</v>
       </c>
       <c r="R21" t="n">
-        <v>6991181</v>
+        <v>6991229</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762585</v>
+        <v>129762566</v>
       </c>
       <c r="B22" t="n">
         <v>57737</v>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472867</v>
+        <v>472716</v>
       </c>
       <c r="R22" t="n">
-        <v>6991229</v>
+        <v>6991137</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73954866</v>
+        <v>129490126</v>
       </c>
       <c r="B2" t="n">
-        <v>94521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1455</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mikroskapania</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scapania carinthiaca</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>J.B.Jack ex Lindb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nygårdens NO-ut mot Haraån, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472782.6141573581</v>
+        <v>472976</v>
       </c>
       <c r="R2" t="n">
-        <v>6991083.734988167</v>
+        <v>6991172</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-10-05</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-10-05</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>EJ FUNNEN men eftersökt i  100mx100m;</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,43 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0 substratenheter</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Eftersök av arter i områden där de inte tidigare är hittade</t>
-        </is>
-      </c>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73954876</v>
+        <v>129490498</v>
       </c>
       <c r="B3" t="n">
-        <v>93160</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>771</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Platt spretmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella turfacea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lindb.) Z.Iwats.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nygårdens NO-ut mot Haraån, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472782.6141573581</v>
+        <v>472965</v>
       </c>
       <c r="R3" t="n">
-        <v>6991083.734988167</v>
+        <v>6991226</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,27 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-10-05</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-10-05</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>EJ FUNNEN men eftersökt i  100mx100m;</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,73 +873,68 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0 substratenheter</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Eftersök av arter i områden där de inte tidigare är hittade</t>
-        </is>
-      </c>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129490714</v>
+        <v>129762633</v>
       </c>
       <c r="B4" t="n">
-        <v>91372</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472905</v>
+        <v>472927</v>
       </c>
       <c r="R4" t="n">
-        <v>6991197</v>
+        <v>6991209</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,22 +961,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I en stående död gran med full längd och som har potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,28 +980,54 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129490126</v>
+        <v>129762634</v>
       </c>
       <c r="B5" t="n">
-        <v>88998</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,34 +1035,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472976</v>
+        <v>472947</v>
       </c>
       <c r="R5" t="n">
-        <v>6991172</v>
+        <v>6991126</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,22 +1096,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,28 +1115,54 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129490826</v>
+        <v>129489731</v>
       </c>
       <c r="B6" t="n">
-        <v>91619</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,19 +1170,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472881</v>
+        <v>472913</v>
       </c>
       <c r="R6" t="n">
-        <v>6991194</v>
+        <v>6991135</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,32 +1266,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129490498</v>
+        <v>129490557</v>
       </c>
       <c r="B7" t="n">
-        <v>91595</v>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472965</v>
+        <v>472950</v>
       </c>
       <c r="R7" t="n">
-        <v>6991226</v>
+        <v>6991212</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,32 +1373,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129489773</v>
+        <v>129490714</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>91680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472910</v>
+        <v>472905</v>
       </c>
       <c r="R8" t="n">
-        <v>6991140</v>
+        <v>6991197</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1443,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,12 +1453,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 individ</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,32 +1480,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129489731</v>
+        <v>129491374</v>
       </c>
       <c r="B9" t="n">
-        <v>91599</v>
+        <v>91680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472913</v>
+        <v>472729</v>
       </c>
       <c r="R9" t="n">
-        <v>6991135</v>
+        <v>6991022</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129489495</v>
+        <v>129762558</v>
       </c>
       <c r="B10" t="n">
-        <v>97661</v>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,34 +1598,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472872</v>
+        <v>472797</v>
       </c>
       <c r="R10" t="n">
-        <v>6991094</v>
+        <v>6991042</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,22 +1659,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>I granstubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,28 +1678,54 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129490374</v>
+        <v>129762657</v>
       </c>
       <c r="B11" t="n">
-        <v>98790</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,43 +1733,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472983</v>
+        <v>472840</v>
       </c>
       <c r="R11" t="n">
-        <v>6991195</v>
+        <v>6991061</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1757,22 +1790,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På en gran bland andra hänglavar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,50 +1809,76 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129490557</v>
+        <v>129489773</v>
       </c>
       <c r="B12" t="n">
-        <v>91372</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1888,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472950</v>
+        <v>472910</v>
       </c>
       <c r="R12" t="n">
-        <v>6991212</v>
+        <v>6991140</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,7 +1923,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1879,7 +1933,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1 individ</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,45 +1965,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129491374</v>
+        <v>129762563</v>
       </c>
       <c r="B13" t="n">
-        <v>91372</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472729</v>
+        <v>472656</v>
       </c>
       <c r="R13" t="n">
-        <v>6991022</v>
+        <v>6991102</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,22 +2042,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,68 +2063,101 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129491664</v>
+        <v>129762564</v>
       </c>
       <c r="B14" t="n">
-        <v>98790</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nattjärnen, Nattjärnen, Jmt</t>
+          <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472699</v>
+        <v>472675</v>
       </c>
       <c r="R14" t="n">
-        <v>6990981</v>
+        <v>6991111</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,22 +2181,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,61 +2202,98 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129491023</v>
+        <v>129762565</v>
       </c>
       <c r="B15" t="n">
-        <v>97661</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472840</v>
+        <v>472694</v>
       </c>
       <c r="R15" t="n">
-        <v>6991159</v>
+        <v>6991118</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,22 +2320,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack/savhack, äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,26 +2341,51 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129762583</v>
+        <v>129762566</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,10 +2429,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472863</v>
+        <v>472716</v>
       </c>
       <c r="R16" t="n">
-        <v>6991225</v>
+        <v>6991137</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2370,10 +2521,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129762584</v>
+        <v>129762567</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,10 +2568,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472871</v>
+        <v>472722</v>
       </c>
       <c r="R17" t="n">
-        <v>6991227</v>
+        <v>6991139</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2509,10 +2660,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129762577</v>
+        <v>129762568</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,10 +2707,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472802</v>
+        <v>472720</v>
       </c>
       <c r="R18" t="n">
-        <v>6991188</v>
+        <v>6991143</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2648,50 +2799,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762624</v>
+        <v>129762569</v>
       </c>
       <c r="B19" t="n">
-        <v>98831</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2703,10 +2846,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472644</v>
+        <v>472728</v>
       </c>
       <c r="R19" t="n">
-        <v>6990960</v>
+        <v>6991144</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2743,7 +2886,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Minst 41 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2752,13 +2895,32 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2776,10 +2938,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762566</v>
+        <v>129762570</v>
       </c>
       <c r="B20" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,10 +2985,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472716</v>
+        <v>472725</v>
       </c>
       <c r="R20" t="n">
-        <v>6991137</v>
+        <v>6991144</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2915,10 +3077,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762575</v>
+        <v>129762571</v>
       </c>
       <c r="B21" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,10 +3124,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472795</v>
+        <v>472735</v>
       </c>
       <c r="R21" t="n">
-        <v>6991181</v>
+        <v>6991146</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3054,10 +3216,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762585</v>
+        <v>129762573</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3101,10 +3263,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472867</v>
+        <v>472776</v>
       </c>
       <c r="R22" t="n">
-        <v>6991229</v>
+        <v>6991166</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3193,10 +3355,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129762579</v>
+        <v>129762574</v>
       </c>
       <c r="B23" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3240,10 +3402,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472826</v>
+        <v>472779</v>
       </c>
       <c r="R23" t="n">
-        <v>6991202</v>
+        <v>6991172</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3332,10 +3494,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129762634</v>
+        <v>129762575</v>
       </c>
       <c r="B24" t="n">
-        <v>91635</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,41 +3505,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472947</v>
+        <v>472795</v>
       </c>
       <c r="R24" t="n">
-        <v>6991126</v>
+        <v>6991181</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3414,7 +3581,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3423,7 +3590,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3444,12 +3610,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3467,52 +3633,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129762558</v>
+        <v>129762576</v>
       </c>
       <c r="B25" t="n">
-        <v>92357</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472797</v>
+        <v>472792</v>
       </c>
       <c r="R25" t="n">
-        <v>6991042</v>
+        <v>6991185</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3549,7 +3720,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I granstubbe.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3558,7 +3729,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3579,12 +3749,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3602,10 +3772,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129762574</v>
+        <v>129762577</v>
       </c>
       <c r="B26" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3649,10 +3819,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>472779</v>
+        <v>472802</v>
       </c>
       <c r="R26" t="n">
-        <v>6991172</v>
+        <v>6991188</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3741,10 +3911,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129762582</v>
+        <v>129762578</v>
       </c>
       <c r="B27" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3788,10 +3958,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472849</v>
+        <v>472809</v>
       </c>
       <c r="R27" t="n">
-        <v>6991219</v>
+        <v>6991191</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3828,7 +3998,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3880,10 +4050,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129762589</v>
+        <v>129762579</v>
       </c>
       <c r="B28" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3927,10 +4097,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472883</v>
+        <v>472826</v>
       </c>
       <c r="R28" t="n">
-        <v>6991239</v>
+        <v>6991202</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4019,10 +4189,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129762586</v>
+        <v>129762580</v>
       </c>
       <c r="B29" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4066,10 +4236,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472881</v>
+        <v>472840</v>
       </c>
       <c r="R29" t="n">
-        <v>6991231</v>
+        <v>6991212</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4106,7 +4276,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på två granstammar nära varann vid hyggeskanten.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4158,10 +4328,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129762657</v>
+        <v>129762581</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4169,37 +4339,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472840</v>
+        <v>472842</v>
       </c>
       <c r="R30" t="n">
-        <v>6991061</v>
+        <v>6991214</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4236,7 +4415,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På en gran bland andra hänglavar.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4245,13 +4424,12 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4266,12 +4444,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4289,10 +4467,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129762568</v>
+        <v>129762582</v>
       </c>
       <c r="B31" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4336,10 +4514,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472720</v>
+        <v>472849</v>
       </c>
       <c r="R31" t="n">
-        <v>6991143</v>
+        <v>6991219</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4376,7 +4554,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack/savhack, färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4428,50 +4606,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129762622</v>
+        <v>129762583</v>
       </c>
       <c r="B32" t="n">
-        <v>98831</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4483,10 +4653,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472814</v>
+        <v>472863</v>
       </c>
       <c r="R32" t="n">
-        <v>6991112</v>
+        <v>6991225</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4523,7 +4693,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4532,13 +4702,32 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4556,10 +4745,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129762570</v>
+        <v>129762584</v>
       </c>
       <c r="B33" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4603,10 +4792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472725</v>
+        <v>472871</v>
       </c>
       <c r="R33" t="n">
-        <v>6991144</v>
+        <v>6991227</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4695,10 +4884,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129762578</v>
+        <v>129762585</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4742,10 +4931,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472809</v>
+        <v>472867</v>
       </c>
       <c r="R34" t="n">
-        <v>6991191</v>
+        <v>6991229</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4834,10 +5023,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129762563</v>
+        <v>129762586</v>
       </c>
       <c r="B35" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4881,10 +5070,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472656</v>
+        <v>472881</v>
       </c>
       <c r="R35" t="n">
-        <v>6991102</v>
+        <v>6991231</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4921,7 +5110,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack/savhack, färska, på två granstammar nära varann vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4973,10 +5162,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762633</v>
+        <v>129762587</v>
       </c>
       <c r="B36" t="n">
-        <v>91635</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4984,41 +5173,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472927</v>
+        <v>472879</v>
       </c>
       <c r="R36" t="n">
-        <v>6991209</v>
+        <v>6991236</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5055,7 +5249,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd och som har potentiella födosökspår efter tretåig hackspett.</t>
+          <t>Ringhack/savhack, färska, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5064,7 +5258,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5085,12 +5278,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5108,10 +5301,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129762590</v>
+        <v>129762588</v>
       </c>
       <c r="B37" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5155,10 +5348,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472886</v>
+        <v>472882</v>
       </c>
       <c r="R37" t="n">
-        <v>6991239</v>
+        <v>6991235</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5247,10 +5440,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129762580</v>
+        <v>129762589</v>
       </c>
       <c r="B38" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5294,10 +5487,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472840</v>
+        <v>472883</v>
       </c>
       <c r="R38" t="n">
-        <v>6991212</v>
+        <v>6991239</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5386,10 +5579,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129762573</v>
+        <v>129762590</v>
       </c>
       <c r="B39" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5433,10 +5626,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472776</v>
+        <v>472886</v>
       </c>
       <c r="R39" t="n">
-        <v>6991166</v>
+        <v>6991239</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5525,10 +5718,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129762565</v>
+        <v>129762591</v>
       </c>
       <c r="B40" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5558,7 +5751,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5572,10 +5765,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>472694</v>
+        <v>472892</v>
       </c>
       <c r="R40" t="n">
-        <v>6991118</v>
+        <v>6991241</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5612,7 +5805,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5664,10 +5857,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129762581</v>
+        <v>129762592</v>
       </c>
       <c r="B41" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5711,10 +5904,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>472842</v>
+        <v>472887</v>
       </c>
       <c r="R41" t="n">
-        <v>6991214</v>
+        <v>6991241</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5803,57 +5996,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129762569</v>
+        <v>129490374</v>
       </c>
       <c r="B42" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Haraån, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472728</v>
+        <v>472983</v>
       </c>
       <c r="R42" t="n">
-        <v>6991144</v>
+        <v>6991195</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5880,17 +6070,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5901,101 +6096,68 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129762576</v>
+        <v>129491664</v>
       </c>
       <c r="B43" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Haraån, Jmt</t>
+          <t>Nattjärnen, Nattjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472792</v>
+        <v>472699</v>
       </c>
       <c r="R43" t="n">
-        <v>6991185</v>
+        <v>6990981</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6019,17 +6181,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6040,83 +6207,66 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129762591</v>
+        <v>129762622</v>
       </c>
       <c r="B44" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6128,10 +6278,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>472892</v>
+        <v>472814</v>
       </c>
       <c r="R44" t="n">
-        <v>6991241</v>
+        <v>6991112</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6168,7 +6318,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6177,32 +6327,13 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6220,42 +6351,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129762571</v>
+        <v>129762624</v>
       </c>
       <c r="B45" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6267,10 +6406,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>472735</v>
+        <v>472644</v>
       </c>
       <c r="R45" t="n">
-        <v>6991146</v>
+        <v>6990960</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6307,7 +6446,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 41 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6316,32 +6455,13 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6359,57 +6479,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129762564</v>
+        <v>129489495</v>
       </c>
       <c r="B46" t="n">
-        <v>57741</v>
+        <v>97983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Haraån, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>472675</v>
+        <v>472872</v>
       </c>
       <c r="R46" t="n">
-        <v>6991111</v>
+        <v>6991094</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6436,17 +6544,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6457,98 +6570,61 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129762592</v>
+        <v>129491023</v>
       </c>
       <c r="B47" t="n">
-        <v>57741</v>
+        <v>97983</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Haraån, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>472887</v>
+        <v>472840</v>
       </c>
       <c r="R47" t="n">
-        <v>6991241</v>
+        <v>6991159</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6575,17 +6651,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6596,461 +6677,19 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>129762567</v>
-      </c>
-      <c r="B48" t="n">
-        <v>57741</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Haraån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>472722</v>
-      </c>
-      <c r="R48" t="n">
-        <v>6991139</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Sunne</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>129762587</v>
-      </c>
-      <c r="B49" t="n">
-        <v>57741</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Haraån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>472879</v>
-      </c>
-      <c r="R49" t="n">
-        <v>6991236</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Sunne</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack/savhack, färska, i riklig mängd på en gran vid hyggeskanten.</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>129762588</v>
-      </c>
-      <c r="B50" t="n">
-        <v>57741</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Haraån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>472882</v>
-      </c>
-      <c r="R50" t="n">
-        <v>6991235</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Sunne</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack/savhack, färska, på en gran vid hyggeskanten.</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49928-2025 artfynd.xlsx
+++ b/artfynd/A 49928-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129490126</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129490498</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762633</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762634</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1263,6 +1288,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129489731</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,6 +1400,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129490557</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1477,6 +1512,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129490714</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129491374</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1719,6 +1764,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762558</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1850,6 +1900,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762657</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1962,6 +2017,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129489773</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2101,6 +2161,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762563</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2240,6 +2305,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762564</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2379,6 +2449,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762565</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2518,6 +2593,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762566</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2657,6 +2737,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762567</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2796,6 +2881,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762568</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2935,6 +3025,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762569</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3074,6 +3169,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762570</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3213,6 +3313,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762571</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3352,6 +3457,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762573</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3491,6 +3601,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762574</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3630,6 +3745,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762575</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3769,6 +3889,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762576</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3908,6 +4033,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762577</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4047,6 +4177,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762578</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4186,6 +4321,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762579</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4325,6 +4465,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762580</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4464,6 +4609,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762581</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4603,6 +4753,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762582</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4742,6 +4897,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762583</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4881,6 +5041,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762584</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5020,6 +5185,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762585</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5159,6 +5329,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762586</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5298,6 +5473,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762587</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5437,6 +5617,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762588</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5576,6 +5761,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762589</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5715,6 +5905,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762590</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5854,6 +6049,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762591</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5993,6 +6193,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762592</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6109,6 +6314,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129490374</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6220,6 +6430,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129491664</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6348,6 +6563,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762622</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6476,6 +6696,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762624</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6583,6 +6808,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129489495</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6690,8 +6920,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129491023</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>